--- a/docs/excel_export_sample.xlsx
+++ b/docs/excel_export_sample.xlsx
@@ -96,7 +96,7 @@
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="46" customWidth="1"/>
+    <col min="10" max="10" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -287,14 +287,14 @@
       <c r="I5"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">服务端标注受限 —— 违反服务条款：This channel is unavailable due to violation of the Terms of Service.</t>
+          <t xml:space="preserve">违反服务条款</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">低价电影票（诈骗）</t>
+          <t xml:space="preserve">低价电影票</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -325,7 +325,7 @@
       <c r="I6"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram 标记该频道为诈骗</t>
+          <t xml:space="preserve">Telegram 官方标记为诈骗 · 色情内容 · 你被禁止发言</t>
         </is>
       </c>
     </row>
@@ -357,7 +357,7 @@
       <c r="I7"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">服务端返回 ChannelForbidden：频道已不可访问（被封 / 被踢 / 频道已删）</t>
+          <t xml:space="preserve">频道已不可访问（被封 / 被踢 / 已删）</t>
         </is>
       </c>
     </row>
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">生成时间 2026-10-15 21:46　范围：样例（演示用数据）（8 行）</t>
+          <t xml:space="preserve">生成时间 2026-10-15 23:29　范围：样例（演示用数据）（8 行）</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -787,7 +787,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">已封禁 / 不可访问</t>
+          <t xml:space="preserve">已封禁</t>
         </is>
       </c>
       <c r="B41" s="2">
@@ -797,17 +797,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">违规受限（版权 / 服务条款 / 色情等）</t>
+          <t xml:space="preserve">违规受限</t>
         </is>
       </c>
       <c r="B42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram 标记：诈骗</t>
+          <t xml:space="preserve">诈骗</t>
         </is>
       </c>
       <c r="B43" s="2">
@@ -817,37 +817,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">对方账号已注销</t>
+          <t xml:space="preserve">禁言</t>
         </is>
       </c>
       <c r="B44" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已注销</t>
+        </is>
+      </c>
+      <c r="B45" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">说明</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">· 用户数 / 作品数 / 活跃时间为空 = 尚未获取（点「获取 / 更新统计」后补全）；</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 「活跃(天前)」显示「无消息」= 该会话里一条消息都没有；</t>
+          <t xml:space="preserve">· 用户数 / 作品数 / 活跃时间为空 = 尚未获取（点「获取 / 更新统计」后补全）；</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 「活跃(天前)」显示「无消息」= 该会话里一条消息都没有；</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">· 本表数据全部来自当前列表，导出时不向 Telegram 发任何请求。</t>
         </is>
@@ -861,11 +871,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="62" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="56" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,7 +902,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">判定依据（服务端字段）</t>
+          <t xml:space="preserve">判定依据</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">服务端原文</t>
         </is>
       </c>
     </row>
@@ -913,19 +929,24 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">违规受限（版权 / 服务条款 / 色情等）</t>
+          <t xml:space="preserve">违规受限</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">服务端标注受限 —— 违反服务条款：This channel is unavailable due to violation of the Terms of Service.</t>
+          <t xml:space="preserve">违反服务条款</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">This channel is unavailable due to violation of the Terms of Service.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">低价电影票（诈骗）</t>
+          <t xml:space="preserve">低价电影票</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -940,19 +961,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram 标记：诈骗</t>
+          <t xml:space="preserve">诈骗</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telegram 标记该频道为诈骗</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Telegram 官方标记为诈骗</t>
+        </is>
+      </c>
+      <c r="F3" s="5"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">已封禁的老频道</t>
+          <t xml:space="preserve">低价电影票</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -962,48 +984,106 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006</t>
+          <t xml:space="preserve">1005</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">已封禁 / 不可访问</t>
+          <t xml:space="preserve">违规受限</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">服务端返回 ChannelForbidden：频道已不可访问（被封 / 被踢 / 频道已删）</t>
-        </is>
-      </c>
+          <t xml:space="preserve">色情内容</t>
+        </is>
+      </c>
+      <c r="F4" s="5"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t xml:space="preserve">低价电影票</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">频道</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1005</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">禁言</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">你被禁止发言</t>
+        </is>
+      </c>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已封禁的老频道</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">频道</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1006</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已封禁</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">频道已不可访问（被封 / 被踢 / 已删）</t>
+        </is>
+      </c>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t xml:space="preserve">7877144361</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t xml:space="preserve">私聊</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">1007</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">对方账号已注销</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已注销</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">对方账号已注销（客户端里是灰头像 / 纯数字名）</t>
         </is>
       </c>
+      <c r="F7" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:F1"/>
 </worksheet>
 </file>